--- a/reports/pdf_rolling5_20260827.xlsx
+++ b/reports/pdf_rolling5_20260827.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,575억   ·   현금 67억(1.4%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 12종목  /  매도 20종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,575억   ·   현금 33억(0.7%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 12종목  /  매도 20종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-425794200</v>
+        <v>-1388914800</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.45%→1.26%</t>
+          <t>4.74%→4.38%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1388914800</v>
+        <v>-425794200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>4.74%→4.38%</t>
+          <t>1.45%→1.26%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1247,23 +1247,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-205964850</v>
+        <v>-404740700</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.49%</t>
+          <t>0.54%→0.42%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>83→76</t>
+          <t>40→33</t>
         </is>
       </c>
     </row>
@@ -1275,23 +1275,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-404740700</v>
+        <v>-205964850</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.42%</t>
+          <t>0.56%→0.49%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>40→33</t>
+          <t>83→76</t>
         </is>
       </c>
     </row>
@@ -1331,23 +1331,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-94278600</v>
+        <v>-403816400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.60%</t>
+          <t>1.68%→1.44%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>120→116</t>
+          <t>69→65</t>
         </is>
       </c>
     </row>
@@ -1359,23 +1359,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-403816400</v>
+        <v>-94278600</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.68%→1.44%</t>
+          <t>0.63%→0.60%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>69→65</t>
+          <t>120→116</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,904억   ·   현금 25억(0.6%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 8종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,904억   ·   현금 12억(0.3%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 8종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,577억   ·   현금 66억(2.5%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 6종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,577억   ·   현금 33억(1.3%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 6종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -2212,7 +2212,7 @@
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,256억   ·   현금 64억(2.8%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 3종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,256억   ·   현금 32억(1.4%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B51" s="4" t="n"/>
@@ -2433,7 +2433,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 4억(1.5%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 12종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 2억(0.7%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 12종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -2851,23 +2851,23 @@
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-22999200</v>
+        <v>-24997200</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.98%</t>
+          <t>0.29%→0.20%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>77→71</t>
+          <t>19→13</t>
         </is>
       </c>
     </row>
@@ -2895,23 +2895,23 @@
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-24997200</v>
+        <v>-22999200</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.29%→0.20%</t>
+          <t>1.09%→0.98%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>19→13</t>
+          <t>77→71</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 561억   ·   현금 6억(1.0%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 4종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 561억   ·   현금 3억(0.5%)      오늘 2026-08-27  vs  5일전 2026-08-20      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B74" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260827.xlsx
+++ b/reports/pdf_rolling5_20260827.xlsx
@@ -2851,23 +2851,23 @@
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-24997200</v>
+        <v>-22999200</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.29%→0.20%</t>
+          <t>1.09%→0.98%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>19→13</t>
+          <t>77→71</t>
         </is>
       </c>
     </row>
@@ -2895,46 +2895,46 @@
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-22999200</v>
+        <v>-24997200</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.98%</t>
+          <t>0.29%→0.20%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>77→71</t>
+          <t>19→13</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>37917600</v>
+        <v>54131000</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>0.84%→0.96%</t>
+          <t>1.00%→1.17%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>42→49</t>
+          <t>35→42</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -2962,23 +2962,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>54131000</v>
+        <v>37917600</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.17%</t>
+          <t>0.84%→0.96%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>35→42</t>
+          <t>42→49</t>
         </is>
       </c>
       <c r="G71" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260827.xlsx
+++ b/reports/pdf_rolling5_20260827.xlsx
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1388914800</v>
+        <v>-425794200</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>4.74%→4.38%</t>
+          <t>1.45%→1.26%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-425794200</v>
+        <v>-1388914800</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.45%→1.26%</t>
+          <t>4.74%→4.38%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1247,23 +1247,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-404740700</v>
+        <v>-205964850</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.42%</t>
+          <t>0.56%→0.49%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>40→33</t>
+          <t>83→76</t>
         </is>
       </c>
     </row>
@@ -1275,23 +1275,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-205964850</v>
+        <v>-404740700</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.49%</t>
+          <t>0.54%→0.42%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>83→76</t>
+          <t>40→33</t>
         </is>
       </c>
     </row>
@@ -2851,23 +2851,23 @@
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-22999200</v>
+        <v>-24997200</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.98%</t>
+          <t>0.29%→0.20%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>77→71</t>
+          <t>19→13</t>
         </is>
       </c>
     </row>
@@ -2895,46 +2895,46 @@
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-24997200</v>
+        <v>-22999200</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.29%→0.20%</t>
+          <t>1.09%→0.98%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>19→13</t>
+          <t>77→71</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>54131000</v>
+        <v>37917600</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.17%</t>
+          <t>0.84%→0.96%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>35→42</t>
+          <t>42→49</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -2962,23 +2962,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>37917600</v>
+        <v>54131000</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>0.84%→0.96%</t>
+          <t>1.00%→1.17%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>42→49</t>
+          <t>35→42</t>
         </is>
       </c>
       <c r="G71" s="17" t="n"/>
